--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486907_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486907_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6983</v>
+        <v>14.6274</v>
       </c>
       <c r="E2" t="n">
-        <v>15.1071</v>
+        <v>15.0955</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4088</v>
+        <v>-0.4681</v>
       </c>
       <c r="G2" t="n">
         <v>5.8497</v>
@@ -610,13 +610,13 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>1.824</v>
+        <v>1.7531</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9141</v>
+        <v>0.9025</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9099</v>
+        <v>0.8506</v>
       </c>
       <c r="V2" t="n">
         <v>6.2032</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0803</v>
+        <v>2.3628</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0555</v>
+        <v>2.1601</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0248</v>
+        <v>0.2027</v>
       </c>
       <c r="G3" t="n">
         <v>0.7944</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.482</v>
+        <v>-0.1995</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4611</v>
+        <v>-0.3565</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0209</v>
+        <v>0.157</v>
       </c>
       <c r="V3" t="n">
         <v>1.7679</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0601</v>
+        <v>1.5698</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4743</v>
+        <v>1.7765</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4142</v>
+        <v>-0.2067</v>
       </c>
       <c r="G4" t="n">
         <v>0.2601</v>
@@ -766,13 +766,13 @@
         <v>3.0801</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1223</v>
+        <v>1.6321</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4144</v>
+        <v>0.7166</v>
       </c>
       <c r="U4" t="n">
-        <v>0.708</v>
+        <v>0.9155</v>
       </c>
       <c r="V4" t="n">
         <v>-1.349</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.3253</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3271</v>
+        <v>1.3814</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.234</v>
+        <v>-1.0561</v>
       </c>
       <c r="G5" t="n">
         <v>1.6341</v>
@@ -844,13 +844,13 @@
         <v>2.6694</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5946</v>
+        <v>1.8267</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0458</v>
+        <v>1.1001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5488</v>
+        <v>0.7266</v>
       </c>
       <c r="V5" t="n">
         <v>-1.6981</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5311</v>
+        <v>-0.6529</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4633</v>
+        <v>-1.1998</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9322</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-3.8911</v>
@@ -922,13 +922,13 @@
         <v>3.0801</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3704</v>
+        <v>1.2485</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0191</v>
+        <v>0.2826</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3513</v>
+        <v>0.9659</v>
       </c>
       <c r="V6" t="n">
         <v>3.0164</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8646</v>
+        <v>-2.3653</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6732</v>
+        <v>-1.0257</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1914</v>
+        <v>-1.3396</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3426</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.862</v>
+        <v>0.3613</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3021</v>
+        <v>-0.0504</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5599</v>
+        <v>0.4117</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1786</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1374</v>
+        <v>-2.55</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.0567</v>
+        <v>-5.1729</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9193</v>
+        <v>2.6229</v>
       </c>
       <c r="G8" t="n">
         <v>-4.1065</v>
@@ -1078,13 +1078,13 @@
         <v>2.4641</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5769</v>
+        <v>1.1642</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5461</v>
+        <v>0.4299</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0308</v>
+        <v>0.7343</v>
       </c>
       <c r="V8" t="n">
         <v>1.0082</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7567</v>
+        <v>-3.1308</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.028</v>
+        <v>-1.6096</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7287</v>
+        <v>-1.5212</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7362</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1252</v>
+        <v>0.5008</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2635</v>
+        <v>0.1549</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1383</v>
+        <v>0.3458</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4579</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3774</v>
+        <v>-4.8429</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.356</v>
+        <v>-0.9104</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0214</v>
+        <v>-3.9325</v>
       </c>
       <c r="G10" t="n">
         <v>-2.261</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2142</v>
+        <v>0.7487</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2249</v>
+        <v>0.2207</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4391</v>
+        <v>0.528</v>
       </c>
       <c r="V10" t="n">
         <v>-3.5359</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1686</v>
+        <v>-5.9298</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8319</v>
+        <v>-2.6227</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3368</v>
+        <v>-3.3071</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9873</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3251</v>
+        <v>-0.0862</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3952</v>
+        <v>-0.186</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0702</v>
+        <v>0.0998</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4189</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.903899999999997</v>
+        <v>-0.5863999999999994</v>
       </c>
       <c r="E12" t="n">
-        <v>6.554900000000003</v>
+        <v>7.872399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.459</v>
+        <v>-8.4588</v>
       </c>
       <c r="G12" t="n">
         <v>-7.7864</v>
@@ -1390,13 +1390,13 @@
         <v>18.4807</v>
       </c>
       <c r="S12" t="n">
-        <v>7.632099999999999</v>
+        <v>8.9497</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8969</v>
+        <v>3.2144</v>
       </c>
       <c r="U12" t="n">
-        <v>5.7354</v>
+        <v>5.735200000000001</v>
       </c>
       <c r="V12" t="n">
         <v>2.3573</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0456</v>
+        <v>7.5582</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6817</v>
+        <v>5.9955</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3639</v>
+        <v>1.5626</v>
       </c>
       <c r="G13" t="n">
         <v>0.1977</v>
@@ -1468,13 +1468,13 @@
         <v>4.1068</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0371</v>
+        <v>-1.5245</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3756</v>
+        <v>-1.0618</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6615</v>
+        <v>-0.4627</v>
       </c>
       <c r="V13" t="n">
         <v>6.8316</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3336</v>
+        <v>2.1907</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3736</v>
+        <v>0.269</v>
       </c>
       <c r="F14" t="n">
-        <v>1.96</v>
+        <v>1.9217</v>
       </c>
       <c r="G14" t="n">
         <v>3.9085</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0759</v>
+        <v>-0.2189</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2171</v>
+        <v>-0.3217</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1413</v>
+        <v>0.1029</v>
       </c>
       <c r="V14" t="n">
         <v>0.3491</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4743</v>
+        <v>1.3418</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7772</v>
+        <v>1.8818</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3029</v>
+        <v>-0.54</v>
       </c>
       <c r="G15" t="n">
         <v>0.8811</v>
@@ -1624,13 +1624,13 @@
         <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3612</v>
+        <v>0.2286</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3952</v>
+        <v>-0.2906</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7564</v>
+        <v>0.5192</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5893</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3578</v>
+        <v>0.8306</v>
       </c>
       <c r="E16" t="n">
-        <v>5.115</v>
+        <v>-0.5976</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7572</v>
+        <v>1.4282</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.112</v>
+        <v>-0.4664</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1188</v>
+        <v>1.0383</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.2308</v>
+        <v>-1.5047</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1074</v>
+        <v>-0.1015</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9496</v>
+        <v>0.4774</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1579</v>
+        <v>-0.579</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2195</v>
+        <v>-0.3649</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8308</v>
+        <v>0.5609</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.3887</v>
+        <v>-0.9257</v>
       </c>
       <c r="P16" t="n">
-        <v>3.0801</v>
+        <v>2.2588</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0801</v>
+        <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.9618</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3485</v>
+        <v>-0.7363</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0204</v>
+        <v>-0.2255</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9384</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6591</v>
+        <v>0.2402</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.5975</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2125</v>
+        <v>0.6989</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2838</v>
+        <v>4.2782</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4962</v>
+        <v>-3.5794</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4664</v>
+        <v>-0.112</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0383</v>
+        <v>2.1188</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5047</v>
+        <v>-2.2308</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1015</v>
+        <v>3.1074</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4774</v>
+        <v>2.9496</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.579</v>
+        <v>0.1579</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3649</v>
+        <v>-3.2195</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5609</v>
+        <v>-0.8308</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9257</v>
+        <v>-2.3887</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2588</v>
+        <v>3.0801</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2588</v>
+        <v>3.0801</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5799</v>
+        <v>-1.3309</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4225</v>
+        <v>-0.4883</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1575</v>
+        <v>-0.8425</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9384</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2402</v>
+        <v>1.6591</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3445</v>
+        <v>0.6339</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.513</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0667</v>
+        <v>1.1469</v>
       </c>
       <c r="G18" t="n">
         <v>2.7722</v>
@@ -1858,13 +1858,13 @@
         <v>2.2588</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2758</v>
+        <v>0.0136</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7246</v>
+        <v>-0.5154</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4488</v>
+        <v>0.529</v>
       </c>
       <c r="V18" t="n">
         <v>-2.3573</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8757</v>
+        <v>-0.9646</v>
       </c>
       <c r="E19" t="n">
         <v>0.3165</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1922</v>
+        <v>-1.2811</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0408</v>
@@ -1936,13 +1936,13 @@
         <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1383</v>
+        <v>0.0494</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2701</v>
+        <v>0.1811</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5893</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6993</v>
+        <v>-1.1477</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0001</v>
+        <v>-0.4738</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6993</v>
+        <v>-0.674</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9101</v>
+        <v>1.4847</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8175</v>
+        <v>2.1637</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9074</v>
+        <v>-0.679</v>
       </c>
       <c r="J20" t="n">
-        <v>6.1372</v>
+        <v>1.7998</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0061</v>
+        <v>2.55</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1311</v>
+        <v>-0.7502</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2271</v>
+        <v>-0.3151</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1887</v>
+        <v>-0.3863</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.0385</v>
+        <v>0.0713</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8481</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.1336</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>3.2855</v>
+        <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8229</v>
+        <v>-0.4272</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2438</v>
+        <v>-0.3721</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.579</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9384</v>
+        <v>-1.1786</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7144</v>
+        <v>-1.2024</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8922</v>
+        <v>0.2093</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8222</v>
+        <v>-1.4117</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4847</v>
+        <v>2.9101</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1637</v>
+        <v>4.8175</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.679</v>
+        <v>-1.9074</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7998</v>
+        <v>6.1372</v>
       </c>
       <c r="K21" t="n">
-        <v>2.55</v>
+        <v>5.0061</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7502</v>
+        <v>1.1311</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3151</v>
+        <v>-3.2271</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3863</v>
+        <v>-0.1887</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0713</v>
+        <v>-3.0385</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0267</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0801</v>
+        <v>-5.1336</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0534</v>
+        <v>3.2855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9938</v>
+        <v>-1.326</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7905</v>
+        <v>-1.0346</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2033</v>
+        <v>-0.2913</v>
       </c>
       <c r="V21" t="n">
+        <v>-0.9384</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="X21" t="n">
         <v>-1.1786</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1786</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-2.3573</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5751</v>
+        <v>-7.3379</v>
       </c>
       <c r="E22" t="n">
         <v>-2.9071</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.668</v>
+        <v>-4.4308</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7486</v>
@@ -2170,13 +2170,13 @@
         <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6745</v>
+        <v>-1.4374</v>
       </c>
       <c r="T22" t="n">
         <v>-0.7827</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8918</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9466</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.903800000000001</v>
+        <v>2.601499999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>8.458699999999999</v>
+        <v>8.458800000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.555</v>
+        <v>-5.857599999999999</v>
       </c>
       <c r="G23" t="n">
         <v>7.7865</v>
@@ -2218,7 +2218,7 @@
         <v>16.1395</v>
       </c>
       <c r="I23" t="n">
-        <v>-8.352999999999998</v>
+        <v>-8.353</v>
       </c>
       <c r="J23" t="n">
         <v>19.4471</v>
@@ -2233,7 +2233,7 @@
         <v>-11.6607</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6523000000000001</v>
+        <v>-0.6522999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-11.0084</v>
@@ -2248,16 +2248,16 @@
         <v>22.5877</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.632300000000001</v>
+        <v>-6.9351</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.7352</v>
+        <v>-5.735200000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8969</v>
+        <v>-1.1996</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.357200000000001</v>
+        <v>-2.3572</v>
       </c>
       <c r="W23" t="n">
         <v>13.2276</v>
